--- a/src/test/resources/testdata/Modules/09_MyWebSite/MyWebSite/01_MyWebSiteTest.xlsx
+++ b/src/test/resources/testdata/Modules/09_MyWebSite/MyWebSite/01_MyWebSiteTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\09_MyWebSite\MyWebSite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4BD51E-CAA2-4533-A187-3543F1B2F20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71063F75-DF33-4AA9-9EC2-CD3DC3180DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -17,11 +17,10 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$N$150</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TestCases!$A$1:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$N$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TestCases!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="552">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -7415,9 +7414,6 @@
     <t>MyWebSiteTest_128</t>
   </si>
   <si>
-    <t>MyWebSiteTest_129</t>
-  </si>
-  <si>
     <t>MyWebSiteTest_130</t>
   </si>
   <si>
@@ -7428,9 +7424,6 @@
   </si>
   <si>
     <t>Projects Page -  If we added 5 images then lable should display as "MAX 5 images allowed" on screen.</t>
-  </si>
-  <si>
-    <t>Projects Page -  If we added  5 images  then Camera capture icon should get disable.</t>
   </si>
   <si>
     <t>Projects Page - While deleting Project images, Delete pop-up should diplay.</t>
@@ -9224,12 +9217,6 @@
   </si>
   <si>
     <t>INPUT_DATA</t>
-  </si>
-  <si>
-    <t>personalinfo_clickon_rolefirmdropfield
-personalinfo_select_rolefirmdropvalue
-clickon_nextbtn
-verify_warningtoastmsg</t>
   </si>
   <si>
     <t>personalinfo_clickon_workprofessionfield
@@ -10102,10 +10089,6 @@
     <t>Please add at least 3 projects</t>
   </si>
   <si>
-    <t>project_clickon_submitbtn
-verify_warningtoastmsg</t>
-  </si>
-  <si>
     <t>project_clickon_fabbtn
 verify_project_showworkwin_title</t>
   </si>
@@ -10127,9 +10110,6 @@
   </si>
   <si>
     <t>PROJECT_BUDGET</t>
-  </si>
-  <si>
-    <t>PROJECT_001</t>
   </si>
   <si>
     <t>project_enter_showworkwin_projectname
@@ -10142,11 +10122,6 @@
   </si>
   <si>
     <t>Enter Area</t>
-  </si>
-  <si>
-    <t>project_clickon_showworwin_stylefield
-project_select_showworwin_styledropvalue
-verify_listwindow_errortoastmsg</t>
   </si>
   <si>
     <t>5666666</t>
@@ -10409,27 +10384,7 @@
 verify_listwindow_count</t>
   </si>
   <si>
-    <t>project_clickon_showworwin_projectphotoicon
-clickon_browsefileoption
-select_gallaryimage
-clickon_gallarydonebtn
-project_clickon_showworwin_projectphotoicon
-clickon_browsefileoption
-select_gallaryimage
-clickon_gallarydonebtn
-project_clickon_showworwin_savebtn
-verify_project_showworwin_imageserror</t>
-  </si>
-  <si>
-    <t>project_addprojectphotos
-project_clickon_showworwin_projectphotoicon
-verify_project_showworwin_imageserror</t>
-  </si>
-  <si>
     <t>Max 5 Images/Videos Allowed</t>
-  </si>
-  <si>
-    <t>verify_project_showworwin_imageicon_isclickable</t>
   </si>
   <si>
     <t>project_clickon_showworwin_deletebtn
@@ -10441,10 +10396,6 @@
   <si>
     <t>project_clickon_showworwin_deletepopup_yesbtn
 verify_project_showworwin_imagescount</t>
-  </si>
-  <si>
-    <t>project_clickon_showworkwin_crossicon
-verify_project_header</t>
   </si>
   <si>
     <t>verify_project_addedprojectname</t>
@@ -10510,6 +10461,122 @@
 project_clickon_showworwin_savebtn
 project_clickon_submitbtn
 verify_warningtoastmsg</t>
+  </si>
+  <si>
+    <t>project_add_projects
+project_clickon_submitbtn
+verify_alert_dialog_title</t>
+  </si>
+  <si>
+    <t>PROJECT</t>
+  </si>
+  <si>
+    <t>project_clickon_fabbtn
+project_clickon_showworwin_projectphotoicon
+clickon_browsefileoption
+select_gallaryimage
+clickon_gallarydonebtn
+project_clickon_showworwin_projectphotoicon
+clickon_browsefileoption
+select_gallaryimage
+clickon_gallarydonebtn
+project_clickon_showworwin_savebtn
+verify_project_showworwin_imageserror</t>
+  </si>
+  <si>
+    <t>project_clickon_showworwin_stylefield
+project_select_showworwin_styledropvalue
+project_clickon_showworwin_savebtn
+verify_listwindow_errortoastmsg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+project_clickon_showworkwin_crossicon
+clickon_alert_dialog_yesbtn
+verify_project_header</t>
+  </si>
+  <si>
+    <t>project_addprojectphotos
+project_clickon_showworwin_projectphotoiconafterselectimage
+verify_project_showworwin_imageserror</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Do you want to submit all details and send for Approval process ?</t>
+  </si>
+  <si>
+    <t>verify_infodialogbox_text</t>
+  </si>
+  <si>
+    <t>clickon_infodialogbox_okbtn
+verify_pagetitle</t>
+  </si>
+  <si>
+    <t>verify_isdraftbtn_display</t>
+  </si>
+  <si>
+    <t>clickon_alert_dialog_yesbtn
+verify_successdialogbox_title</t>
+  </si>
+  <si>
+    <t>verify_successdialogbox_text</t>
+  </si>
+  <si>
+    <t>clickon_successdialogbox_okbtn
+verify_infodialogbox_title</t>
+  </si>
+  <si>
+    <t>Information</t>
+  </si>
+  <si>
+    <t>To help complete your video upload in the background, keep your internet on and avoid using power saving mode.</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>clickon_nextbtn
+clickon_nextbtn
+verify_warningtoastmsg</t>
+  </si>
+  <si>
+    <t>personalinfo_clickon_rolefirmdropfield
+personalinfo_select_rolefirmdropvalue
+clickon_nextbtn
+clickon_nextbtn
+verify_warningtoastmsg</t>
+  </si>
+  <si>
+    <t>Faridkot,Amritsar</t>
+  </si>
+  <si>
+    <t>Do you want to save this details? You will not be able to edit it later.</t>
+  </si>
+  <si>
+    <t>Firm Details</t>
+  </si>
+  <si>
+    <t>Enter Your Firm/Office Name</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>Your website details saved successfully.</t>
+  </si>
+  <si>
+    <t>project_clickon_submitbtn
+project_clickon_submitbtn
+verify_warningtoastmsg</t>
+  </si>
+  <si>
+    <t>verify_mywebsite_webversion_status
+navigatebacktodashboardpage</t>
   </si>
 </sst>
 </file>
@@ -10671,7 +10738,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10866,12 +10933,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -11082,7 +11143,9 @@
     <xf numFmtId="49" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -11459,7 +11522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N149"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" style="2" customWidth="1"/>
@@ -11473,7 +11536,7 @@
     <col min="9" max="9" width="21.36328125" style="2" customWidth="1"/>
     <col min="10" max="11" width="33.36328125" style="2" customWidth="1"/>
     <col min="12" max="12" width="21.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="53.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="91.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10" style="2" customWidth="1"/>
     <col min="15" max="16384" width="8.90625" style="2"/>
   </cols>
@@ -11495,22 +11558,22 @@
         <v>3</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="L1" s="9" t="s">
         <v>9</v>
@@ -11522,31 +11585,31 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="1" t="s">
-        <v>468</v>
+      <c r="C2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3" t="s">
+        <v>285</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>5</v>
@@ -11559,24 +11622,24 @@
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>218</v>
+      <c r="C3" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>224</v>
+        <v>14</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
+        <v>332</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
       <c r="L3" s="5"/>
       <c r="M3" s="1" t="s">
-        <v>471</v>
+        <v>286</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>5</v>
@@ -11589,154 +11652,144 @@
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>219</v>
+      <c r="C4" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>225</v>
+        <v>15</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>472</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+        <v>333</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
       <c r="L4" s="5"/>
       <c r="M4" s="1" t="s">
-        <v>321</v>
+        <v>287</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>220</v>
+      <c r="C5" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>226</v>
+        <v>16</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+        <v>334</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="1" t="s">
-        <v>479</v>
+      <c r="M5" s="3" t="s">
+        <v>285</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>234</v>
+      <c r="C6" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>227</v>
+        <v>17</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>481</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
+        <v>335</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
       <c r="L6" s="5"/>
       <c r="M6" s="1" t="s">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>235</v>
+      <c r="C7" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>228</v>
+        <v>290</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="K7" s="1"/>
+        <v>336</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
       <c r="L7" s="5"/>
       <c r="M7" s="1" t="s">
-        <v>483</v>
+        <v>289</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>236</v>
+      <c r="C8" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>229</v>
+        <v>291</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>484</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
       <c r="L8" s="5"/>
       <c r="M8" s="1" t="s">
-        <v>485</v>
+        <v>288</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>5</v>
@@ -11749,46 +11802,44 @@
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>237</v>
+      <c r="C9" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>230</v>
+        <v>292</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>454</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
       <c r="L9" s="5"/>
-      <c r="M9" s="1" t="s">
-        <v>488</v>
+      <c r="M9" s="3" t="s">
+        <v>285</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>238</v>
+      <c r="C10" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>490</v>
+        <v>309</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -11797,28 +11848,28 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="5"/>
-      <c r="M10" s="2" t="s">
-        <v>491</v>
+      <c r="M10" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>239</v>
+      <c r="C11" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>492</v>
+        <v>18</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -11828,89 +11879,91 @@
       <c r="K11" s="1"/>
       <c r="L11" s="5"/>
       <c r="M11" s="1" t="s">
-        <v>471</v>
+        <v>311</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>240</v>
+      <c r="C12" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>233</v>
+        <v>341</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+        <v>342</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
       <c r="L12" s="5"/>
       <c r="M12" s="1" t="s">
-        <v>467</v>
+        <v>312</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="145" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>241</v>
+      <c r="C13" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>246</v>
+        <v>293</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>514</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+        <v>343</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
       <c r="L13" s="5"/>
       <c r="M13" s="1" t="s">
-        <v>488</v>
+        <v>314</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>242</v>
+      <c r="C14" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="F14" s="1"/>
+        <v>491</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>344</v>
+      </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -11918,27 +11971,27 @@
       <c r="K14" s="1"/>
       <c r="L14" s="5"/>
       <c r="M14" s="1" t="s">
-        <v>516</v>
+        <v>315</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>243</v>
+      <c r="C15" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>517</v>
+        <v>295</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>543</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -11948,27 +12001,27 @@
       <c r="K15" s="1"/>
       <c r="L15" s="5"/>
       <c r="M15" s="1" t="s">
-        <v>10</v>
+        <v>316</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>244</v>
+      <c r="C16" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>518</v>
+        <v>346</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -11978,7 +12031,7 @@
       <c r="K16" s="1"/>
       <c r="L16" s="5"/>
       <c r="M16" s="1" t="s">
-        <v>519</v>
+        <v>317</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>5</v>
@@ -11991,14 +12044,14 @@
       <c r="B17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>245</v>
+      <c r="C17" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>250</v>
+        <v>297</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>520</v>
+        <v>347</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -12008,7 +12061,7 @@
       <c r="K17" s="1"/>
       <c r="L17" s="5"/>
       <c r="M17" s="1" t="s">
-        <v>454</v>
+        <v>318</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>5</v>
@@ -12021,16 +12074,18 @@
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>252</v>
+      <c r="C18" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="F18" s="1"/>
+        <v>349</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>348</v>
+      </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -12038,93 +12093,90 @@
       <c r="K18" s="1"/>
       <c r="L18" s="5"/>
       <c r="M18" s="1" t="s">
-        <v>467</v>
+        <v>350</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="232" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>253</v>
+      <c r="C19" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>259</v>
+        <v>299</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>523</v>
-      </c>
-      <c r="F19" s="1"/>
+        <v>351</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>352</v>
+      </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-      <c r="I19" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>530</v>
-      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
       <c r="L19" s="5"/>
       <c r="M19" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>254</v>
+      <c r="C20" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
+        <v>300</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>398</v>
+      </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="M20" s="1"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="1" t="s">
+        <v>319</v>
+      </c>
       <c r="N20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>255</v>
+      <c r="C21" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>524</v>
+        <v>301</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>353</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -12132,59 +12184,63 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="M21" s="1"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="15" t="s">
+        <v>312</v>
+      </c>
       <c r="N21" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>256</v>
+      <c r="C22" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="F22" s="1"/>
+        <v>302</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>354</v>
+      </c>
       <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
+      <c r="H22" s="1" t="s">
+        <v>355</v>
+      </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="M22" s="1"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="15" t="s">
+        <v>357</v>
+      </c>
       <c r="N22" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>257</v>
+      <c r="C23" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>526</v>
+        <v>303</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>358</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -12192,10 +12248,10 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="M23" s="1"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="15" t="s">
+        <v>544</v>
+      </c>
       <c r="N23" s="1" t="s">
         <v>5</v>
       </c>
@@ -12207,14 +12263,14 @@
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>258</v>
+      <c r="C24" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>264</v>
+        <v>304</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>531</v>
+        <v>359</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -12223,8 +12279,8 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="5"/>
-      <c r="M24" s="1" t="s">
-        <v>519</v>
+      <c r="M24" s="15" t="s">
+        <v>321</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>5</v>
@@ -12237,14 +12293,14 @@
       <c r="B25" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>276</v>
+      <c r="C25" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>265</v>
+        <v>305</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>532</v>
+        <v>360</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -12253,44 +12309,38 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="5"/>
-      <c r="M25" s="1" t="s">
-        <v>10</v>
+      <c r="M25" s="15" t="s">
+        <v>312</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" ht="87" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>277</v>
+      <c r="C26" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>266</v>
+        <v>306</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>533</v>
+        <v>362</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-      <c r="I26" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>530</v>
-      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
       <c r="L26" s="5"/>
-      <c r="M26" s="1" t="s">
-        <v>468</v>
+      <c r="M26" s="15" t="s">
+        <v>321</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>5</v>
@@ -12303,13 +12353,15 @@
       <c r="B27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>278</v>
+      <c r="C27" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="E27" s="1"/>
+        <v>307</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>361</v>
+      </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -12317,25 +12369,29 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="5"/>
-      <c r="M27" s="1"/>
+      <c r="M27" s="15" t="s">
+        <v>545</v>
+      </c>
       <c r="N27" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>279</v>
+      <c r="C28" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="E28" s="1"/>
+        <v>308</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>363</v>
+      </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -12343,25 +12399,29 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="1"/>
+      <c r="M28" s="15" t="s">
+        <v>546</v>
+      </c>
       <c r="N28" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>280</v>
+      <c r="C29" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="E29" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>336</v>
+      </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -12369,25 +12429,29 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="5"/>
-      <c r="M29" s="1"/>
+      <c r="M29" s="15" t="s">
+        <v>289</v>
+      </c>
       <c r="N29" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>281</v>
+      <c r="C30" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="E30" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -12395,25 +12459,29 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="5"/>
-      <c r="M30" s="1"/>
+      <c r="M30" s="15" t="s">
+        <v>285</v>
+      </c>
       <c r="N30" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>282</v>
+      <c r="C31" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="E31" s="1"/>
+        <v>364</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>365</v>
+      </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -12421,25 +12489,29 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="5"/>
-      <c r="M31" s="1"/>
+      <c r="M31" s="15" t="s">
+        <v>546</v>
+      </c>
       <c r="N31" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>283</v>
+      <c r="C32" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="E32" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>343</v>
+      </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -12447,7 +12519,9 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="5"/>
-      <c r="M32" s="1"/>
+      <c r="M32" s="15" t="s">
+        <v>547</v>
+      </c>
       <c r="N32" s="1" t="s">
         <v>5</v>
       </c>
@@ -12459,13 +12533,15 @@
       <c r="B33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>284</v>
+      <c r="C33" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="E33" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>366</v>
+      </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -12473,25 +12549,29 @@
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="5"/>
-      <c r="M33" s="1"/>
+      <c r="M33" s="15" t="s">
+        <v>10</v>
+      </c>
       <c r="N33" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>285</v>
+      <c r="C34" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="E34" s="1"/>
+        <v>323</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>367</v>
+      </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -12499,25 +12579,29 @@
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="5"/>
-      <c r="M34" s="1"/>
+      <c r="M34" s="15" t="s">
+        <v>10</v>
+      </c>
       <c r="N34" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>286</v>
+      <c r="C35" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="E35" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>368</v>
+      </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -12525,13 +12609,3575 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="5"/>
-      <c r="M35" s="1"/>
+      <c r="M35" s="15" t="s">
+        <v>319</v>
+      </c>
       <c r="N35" s="1" t="s">
         <v>5</v>
       </c>
     </row>
+    <row r="36" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="G52" s="6"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="G53" s="6"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="5"/>
+      <c r="M57" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A58" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="5"/>
+      <c r="M58" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="5"/>
+      <c r="M60" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A62" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="5"/>
+      <c r="M62" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A64" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="5"/>
+      <c r="M64" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
+      <c r="I65" s="12"/>
+      <c r="J65" s="12"/>
+      <c r="K65" s="12"/>
+      <c r="L65" s="12"/>
+      <c r="M65" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A66" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="5"/>
+      <c r="M66" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="5"/>
+      <c r="M67" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A68" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A69" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="5"/>
+      <c r="M71" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="F72" s="14" t="s">
+        <v>498</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A73" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="F73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="F74" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" s="8" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A76" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="12"/>
+      <c r="K76" s="12"/>
+      <c r="L76" s="12"/>
+      <c r="M76" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A77" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="5"/>
+      <c r="M77" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A78" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="5"/>
+      <c r="M78" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A79" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="5"/>
+      <c r="M79" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A80" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="5"/>
+      <c r="M80" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="N80" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A81" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="5"/>
+      <c r="M81" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A82" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="5"/>
+      <c r="M82" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A83" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="F83" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="5"/>
+      <c r="M83" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N83" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A84" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="F84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="5"/>
+      <c r="M84" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A85" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="F85" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="5"/>
+      <c r="M85" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="N85" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A86" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="5"/>
+      <c r="M86" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A87" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E87" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+      <c r="H87" s="12"/>
+      <c r="I87" s="12"/>
+      <c r="J87" s="12"/>
+      <c r="K87" s="12"/>
+      <c r="L87" s="12"/>
+      <c r="M87" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="N87" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A88" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="5"/>
+      <c r="M88" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="N88" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A89" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="5"/>
+      <c r="M89" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A90" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="5"/>
+      <c r="M90" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="N90" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A91" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="5"/>
+      <c r="M91" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A92" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="5"/>
+      <c r="M92" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A93" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="5"/>
+      <c r="M93" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A94" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="F94" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="5"/>
+      <c r="M94" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A95" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="F95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="5"/>
+      <c r="M95" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A96" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="F96" s="14" t="s">
+        <v>502</v>
+      </c>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
+      <c r="K96" s="1"/>
+      <c r="L96" s="5"/>
+      <c r="M96" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A97" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="5"/>
+      <c r="M97" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A98" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="5"/>
+      <c r="L98" s="5"/>
+      <c r="M98" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A99" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
+      <c r="K99" s="1"/>
+      <c r="L99" s="5"/>
+      <c r="M99" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" s="8" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A100" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E100" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
+      <c r="H100" s="12"/>
+      <c r="I100" s="12"/>
+      <c r="J100" s="12"/>
+      <c r="K100" s="12"/>
+      <c r="L100" s="12"/>
+      <c r="M100" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="N100" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A101" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="5"/>
+      <c r="M101" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A102" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
+      <c r="K102" s="1"/>
+      <c r="L102" s="5"/>
+      <c r="M102" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="N102" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A103" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
+      <c r="K103" s="1"/>
+      <c r="L103" s="5"/>
+      <c r="M103" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A104" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
+      <c r="K104" s="1"/>
+      <c r="L104" s="5"/>
+      <c r="M104" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="N104" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A105" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
+      <c r="K105" s="1"/>
+      <c r="L105" s="5"/>
+      <c r="M105" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="N105" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A106" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
+      <c r="K106" s="1"/>
+      <c r="L106" s="5"/>
+      <c r="M106" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A107" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1"/>
+      <c r="K107" s="1"/>
+      <c r="L107" s="5"/>
+      <c r="M107" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="N107" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A108" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="F108" s="1"/>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
+      <c r="K108" s="1"/>
+      <c r="L108" s="5"/>
+      <c r="M108" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A109" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="L109" s="5"/>
+      <c r="M109" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="N109" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A110" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="L110" s="5"/>
+      <c r="M110" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="N110" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A111" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
+      <c r="K111" s="1"/>
+      <c r="L111" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="M111" s="1"/>
+      <c r="N111" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A112" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
+      <c r="K112" s="1"/>
+      <c r="L112" s="5"/>
+      <c r="M112" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="N112" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A113" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
+      <c r="K113" s="1"/>
+      <c r="L113" s="5"/>
+      <c r="M113" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="N113" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A114" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
+      <c r="K114" s="1"/>
+      <c r="L114" s="5"/>
+      <c r="M114" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N114" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A115" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
+      <c r="K115" s="1"/>
+      <c r="L115" s="5"/>
+      <c r="M115" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="N115" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A116" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="E116" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1"/>
+      <c r="K116" s="1"/>
+      <c r="L116" s="5"/>
+      <c r="M116" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="N116" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A117" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
+      <c r="K117" s="1"/>
+      <c r="L117" s="5"/>
+      <c r="M117" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="N117" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A118" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1"/>
+      <c r="K118" s="1"/>
+      <c r="L118" s="5"/>
+      <c r="M118" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="N118" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A119" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="F119" s="1"/>
+      <c r="G119" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1"/>
+      <c r="K119" s="1"/>
+      <c r="L119" s="5"/>
+      <c r="M119" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N119" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A120" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F120" s="1"/>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="J120" s="1"/>
+      <c r="K120" s="1"/>
+      <c r="L120" s="5"/>
+      <c r="M120" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="N120" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A121" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F121" s="1"/>
+      <c r="G121" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="H121" s="1"/>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1"/>
+      <c r="K121" s="1"/>
+      <c r="L121" s="5"/>
+      <c r="M121" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A122" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="K122" s="1"/>
+      <c r="L122" s="5"/>
+      <c r="M122" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="N122" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A123" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1"/>
+      <c r="K123" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="L123" s="5"/>
+      <c r="M123" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="N123" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A124" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="F124" s="1"/>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1"/>
+      <c r="K124" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="L124" s="5"/>
+      <c r="M124" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="N124" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A125" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="F125" s="1"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+      <c r="J125" s="1"/>
+      <c r="K125" s="1"/>
+      <c r="L125" s="5"/>
+      <c r="M125" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="N125" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A126" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="F126" s="1"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
+      <c r="K126" s="1"/>
+      <c r="L126" s="5"/>
+      <c r="M126" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="N126" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A127" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="F127" s="1"/>
+      <c r="G127" s="1"/>
+      <c r="H127" s="1"/>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1"/>
+      <c r="K127" s="1"/>
+      <c r="L127" s="5"/>
+      <c r="M127" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="N127" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A128" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
+      <c r="K128" s="1"/>
+      <c r="L128" s="5"/>
+      <c r="M128" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="N128" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A129" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
+      <c r="K129" s="1"/>
+      <c r="L129" s="5"/>
+      <c r="M129" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="N129" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A130" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="F130" s="1"/>
+      <c r="G130" s="1"/>
+      <c r="H130" s="1"/>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1"/>
+      <c r="K130" s="1"/>
+      <c r="L130" s="5"/>
+      <c r="M130" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="N130" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A131" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="F131" s="1"/>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1"/>
+      <c r="K131" s="1"/>
+      <c r="L131" s="5"/>
+      <c r="M131" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="N131" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A132" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F132" s="1"/>
+      <c r="G132" s="1"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1"/>
+      <c r="K132" s="1"/>
+      <c r="L132" s="5"/>
+      <c r="M132" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="N132" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" ht="232" x14ac:dyDescent="0.35">
+      <c r="A133" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="F133" s="1"/>
+      <c r="G133" s="1"/>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="L133" s="5"/>
+      <c r="M133" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N133" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A134" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F134" s="1"/>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
+      <c r="K134" s="1"/>
+      <c r="L134" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="M134" s="1"/>
+      <c r="N134" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A135" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="F135" s="1"/>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1"/>
+      <c r="I135" s="1"/>
+      <c r="J135" s="1"/>
+      <c r="K135" s="1"/>
+      <c r="L135" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="M135" s="1"/>
+      <c r="N135" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A136" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
+      <c r="K136" s="1"/>
+      <c r="L136" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="M136" s="1"/>
+      <c r="N136" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A137" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="F137" s="1"/>
+      <c r="G137" s="1"/>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1"/>
+      <c r="K137" s="1"/>
+      <c r="L137" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="M137" s="1"/>
+      <c r="N137" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A138" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="F138" s="1"/>
+      <c r="G138" s="1"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+      <c r="J138" s="1"/>
+      <c r="K138" s="1"/>
+      <c r="L138" s="5"/>
+      <c r="M138" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="N138" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A139" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="F139" s="1"/>
+      <c r="G139" s="1"/>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1"/>
+      <c r="J139" s="1"/>
+      <c r="K139" s="1"/>
+      <c r="L139" s="5"/>
+      <c r="M139" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N139" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A140" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="F140" s="1"/>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="L140" s="5"/>
+      <c r="M140" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="N140" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A141" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="F141" s="1"/>
+      <c r="G141" s="1"/>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="K141" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="L141" s="5"/>
+      <c r="M141" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="N141" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A142" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="F142" s="1"/>
+      <c r="G142" s="1"/>
+      <c r="H142" s="1"/>
+      <c r="I142" s="1"/>
+      <c r="J142" s="1"/>
+      <c r="K142" s="1"/>
+      <c r="L142" s="5"/>
+      <c r="M142" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="N142" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A143" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="F143" s="1"/>
+      <c r="G143" s="1"/>
+      <c r="H143" s="1"/>
+      <c r="I143" s="1"/>
+      <c r="J143" s="1"/>
+      <c r="K143" s="1"/>
+      <c r="L143" s="5"/>
+      <c r="M143" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="N143" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A144" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="F144" s="1"/>
+      <c r="G144" s="1"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+      <c r="J144" s="1"/>
+      <c r="K144" s="1"/>
+      <c r="L144" s="5"/>
+      <c r="M144" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="N144" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A145" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="F145" s="1"/>
+      <c r="G145" s="1"/>
+      <c r="H145" s="1"/>
+      <c r="I145" s="1"/>
+      <c r="J145" s="1"/>
+      <c r="K145" s="1"/>
+      <c r="L145" s="5"/>
+      <c r="M145" s="15" t="s">
+        <v>539</v>
+      </c>
+      <c r="N145" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A146" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="F146" s="1"/>
+      <c r="G146" s="1"/>
+      <c r="H146" s="1"/>
+      <c r="I146" s="1"/>
+      <c r="J146" s="1"/>
+      <c r="K146" s="1"/>
+      <c r="L146" s="5"/>
+      <c r="M146" s="15" t="s">
+        <v>540</v>
+      </c>
+      <c r="N146" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A147" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="F147" s="1"/>
+      <c r="G147" s="1"/>
+      <c r="H147" s="1"/>
+      <c r="I147" s="1"/>
+      <c r="J147" s="1"/>
+      <c r="K147" s="1"/>
+      <c r="L147" s="5"/>
+      <c r="M147" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="N147" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A148" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="F148" s="1"/>
+      <c r="G148" s="1"/>
+      <c r="H148" s="1"/>
+      <c r="I148" s="1"/>
+      <c r="J148" s="1"/>
+      <c r="K148" s="1"/>
+      <c r="L148" s="5"/>
+      <c r="M148" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="N148" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A149" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="F149" s="1"/>
+      <c r="G149" s="1"/>
+      <c r="H149" s="1"/>
+      <c r="I149" s="1"/>
+      <c r="J149" s="1"/>
+      <c r="K149" s="1"/>
+      <c r="L149" s="5"/>
+      <c r="M149" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="N149" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N13" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}"/>
+  <autoFilter ref="A1:N1" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}"/>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -12540,7 +16186,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A0187B-E061-4912-A527-D651D3F0111B}">
-  <dimension ref="A1:N150"/>
+  <dimension ref="A1:N149"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" style="2" customWidth="1"/>
@@ -12554,7 +16200,7 @@
     <col min="9" max="9" width="21.36328125" style="2" customWidth="1"/>
     <col min="10" max="11" width="33.36328125" style="2" customWidth="1"/>
     <col min="12" max="12" width="21.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.453125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="91.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10" style="2" customWidth="1"/>
     <col min="15" max="16384" width="8.90625" style="2"/>
   </cols>
@@ -12576,22 +16222,22 @@
         <v>3</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="L1" s="9" t="s">
         <v>9</v>
@@ -12610,14 +16256,14 @@
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -12627,7 +16273,7 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>5</v>
@@ -12640,14 +16286,14 @@
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="5" t="s">
         <v>91</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -12657,7 +16303,7 @@
       <c r="K3" s="6"/>
       <c r="L3" s="5"/>
       <c r="M3" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>5</v>
@@ -12670,14 +16316,14 @@
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="5" t="s">
         <v>92</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -12687,7 +16333,7 @@
       <c r="K4" s="6"/>
       <c r="L4" s="5"/>
       <c r="M4" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>5</v>
@@ -12700,14 +16346,14 @@
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="5" t="s">
         <v>93</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -12717,7 +16363,7 @@
       <c r="K5" s="6"/>
       <c r="L5" s="5"/>
       <c r="M5" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>5</v>
@@ -12730,14 +16376,14 @@
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="5" t="s">
         <v>94</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -12747,7 +16393,7 @@
       <c r="K6" s="6"/>
       <c r="L6" s="5"/>
       <c r="M6" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>5</v>
@@ -12760,14 +16406,14 @@
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="5" t="s">
         <v>95</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -12777,7 +16423,7 @@
       <c r="K7" s="6"/>
       <c r="L7" s="5"/>
       <c r="M7" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>5</v>
@@ -12790,14 +16436,14 @@
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="5" t="s">
         <v>96</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -12807,7 +16453,7 @@
       <c r="K8" s="6"/>
       <c r="L8" s="5"/>
       <c r="M8" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>5</v>
@@ -12820,14 +16466,14 @@
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="5" t="s">
         <v>97</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -12837,7 +16483,7 @@
       <c r="K9" s="6"/>
       <c r="L9" s="5"/>
       <c r="M9" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>5</v>
@@ -12850,14 +16496,14 @@
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="5" t="s">
         <v>98</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -12867,7 +16513,7 @@
       <c r="K10" s="1"/>
       <c r="L10" s="5"/>
       <c r="M10" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>5</v>
@@ -12880,14 +16526,14 @@
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="5" t="s">
         <v>99</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -12897,7 +16543,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="5"/>
       <c r="M11" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>5</v>
@@ -12910,14 +16556,14 @@
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="5" t="s">
         <v>100</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
@@ -12927,7 +16573,7 @@
       <c r="K12" s="6"/>
       <c r="L12" s="5"/>
       <c r="M12" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>5</v>
@@ -12940,14 +16586,14 @@
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="5" t="s">
         <v>101</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
@@ -12957,7 +16603,7 @@
       <c r="K13" s="6"/>
       <c r="L13" s="5"/>
       <c r="M13" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>5</v>
@@ -12970,17 +16616,17 @@
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="5" t="s">
         <v>102</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -12989,27 +16635,27 @@
       <c r="K14" s="1"/>
       <c r="L14" s="5"/>
       <c r="M14" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="5" t="s">
         <v>103</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>348</v>
+        <v>543</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -13019,7 +16665,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="5"/>
       <c r="M15" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>5</v>
@@ -13032,14 +16678,14 @@
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="5" t="s">
         <v>104</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -13049,7 +16695,7 @@
       <c r="K16" s="1"/>
       <c r="L16" s="5"/>
       <c r="M16" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>5</v>
@@ -13062,14 +16708,14 @@
       <c r="B17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="5" t="s">
         <v>105</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -13079,7 +16725,7 @@
       <c r="K17" s="1"/>
       <c r="L17" s="5"/>
       <c r="M17" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>5</v>
@@ -13092,17 +16738,17 @@
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="5" t="s">
         <v>106</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -13111,7 +16757,7 @@
       <c r="K18" s="1"/>
       <c r="L18" s="5"/>
       <c r="M18" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>5</v>
@@ -13124,17 +16770,17 @@
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="5" t="s">
         <v>107</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -13143,7 +16789,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="5"/>
       <c r="M19" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>5</v>
@@ -13156,17 +16802,17 @@
       <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="5" t="s">
         <v>108</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -13174,7 +16820,7 @@
       <c r="K20" s="1"/>
       <c r="L20" s="5"/>
       <c r="M20" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>5</v>
@@ -13187,14 +16833,14 @@
       <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="5" t="s">
         <v>109</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -13203,8 +16849,8 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="5"/>
-      <c r="M21" s="1" t="s">
-        <v>400</v>
+      <c r="M21" s="15" t="s">
+        <v>312</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>5</v>
@@ -13217,28 +16863,28 @@
       <c r="B22" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="5" t="s">
         <v>110</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="5"/>
-      <c r="M22" s="1" t="s">
-        <v>407</v>
+      <c r="M22" s="15" t="s">
+        <v>357</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>5</v>
@@ -13251,14 +16897,14 @@
       <c r="B23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="5" t="s">
         <v>111</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -13267,8 +16913,8 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="5"/>
-      <c r="M23" s="1" t="s">
-        <v>407</v>
+      <c r="M23" s="15" t="s">
+        <v>544</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>5</v>
@@ -13281,14 +16927,14 @@
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="5" t="s">
         <v>112</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -13297,8 +16943,8 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="5"/>
-      <c r="M24" s="1" t="s">
-        <v>420</v>
+      <c r="M24" s="15" t="s">
+        <v>321</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>5</v>
@@ -13311,14 +16957,14 @@
       <c r="B25" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -13327,8 +16973,8 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="5"/>
-      <c r="M25" s="1" t="s">
-        <v>421</v>
+      <c r="M25" s="15" t="s">
+        <v>312</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>5</v>
@@ -13341,14 +16987,14 @@
       <c r="B26" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="5" t="s">
         <v>114</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -13357,8 +17003,8 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="5"/>
-      <c r="M26" s="1" t="s">
-        <v>421</v>
+      <c r="M26" s="15" t="s">
+        <v>321</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>5</v>
@@ -13371,14 +17017,14 @@
       <c r="B27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="5" t="s">
         <v>115</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -13387,8 +17033,8 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="5"/>
-      <c r="M27" s="1" t="s">
-        <v>400</v>
+      <c r="M27" s="15" t="s">
+        <v>545</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>5</v>
@@ -13401,14 +17047,14 @@
       <c r="B28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="5" t="s">
         <v>116</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -13417,8 +17063,8 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="1" t="s">
-        <v>407</v>
+      <c r="M28" s="15" t="s">
+        <v>546</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>5</v>
@@ -13431,14 +17077,14 @@
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="5" t="s">
         <v>117</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -13447,8 +17093,8 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="5"/>
-      <c r="M29" s="1" t="s">
-        <v>407</v>
+      <c r="M29" s="15" t="s">
+        <v>289</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>5</v>
@@ -13461,14 +17107,14 @@
       <c r="B30" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="5" t="s">
         <v>118</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -13477,8 +17123,8 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="5"/>
-      <c r="M30" s="1" t="s">
-        <v>400</v>
+      <c r="M30" s="15" t="s">
+        <v>285</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>5</v>
@@ -13491,14 +17137,14 @@
       <c r="B31" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="5" t="s">
         <v>119</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -13507,8 +17153,8 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="5"/>
-      <c r="M31" s="1" t="s">
-        <v>407</v>
+      <c r="M31" s="15" t="s">
+        <v>546</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>5</v>
@@ -13521,14 +17167,14 @@
       <c r="B32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="5" t="s">
         <v>120</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -13537,8 +17183,8 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="5"/>
-      <c r="M32" s="1" t="s">
-        <v>407</v>
+      <c r="M32" s="15" t="s">
+        <v>547</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>5</v>
@@ -13551,14 +17197,14 @@
       <c r="B33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="5" t="s">
         <v>121</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -13567,8 +17213,8 @@
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="5"/>
-      <c r="M33" s="1" t="s">
-        <v>315</v>
+      <c r="M33" s="15" t="s">
+        <v>10</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>5</v>
@@ -13581,14 +17227,14 @@
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="5" t="s">
         <v>122</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -13597,7 +17243,7 @@
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="5"/>
-      <c r="M34" s="1" t="s">
+      <c r="M34" s="15" t="s">
         <v>10</v>
       </c>
       <c r="N34" s="1" t="s">
@@ -13611,14 +17257,14 @@
       <c r="B35" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="5" t="s">
         <v>123</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -13627,8 +17273,8 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="5"/>
-      <c r="M35" s="2" t="s">
-        <v>321</v>
+      <c r="M35" s="15" t="s">
+        <v>319</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>5</v>
@@ -13641,14 +17287,14 @@
       <c r="B36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="5" t="s">
         <v>124</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -13657,8 +17303,8 @@
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="5"/>
-      <c r="M36" s="2" t="s">
-        <v>321</v>
+      <c r="M36" s="15" t="s">
+        <v>319</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>5</v>
@@ -13671,17 +17317,17 @@
       <c r="B37" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
@@ -13689,8 +17335,8 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="5"/>
-      <c r="M37" s="1" t="s">
-        <v>324</v>
+      <c r="M37" s="15" t="s">
+        <v>322</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>5</v>
@@ -13703,17 +17349,17 @@
       <c r="B38" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="5" t="s">
         <v>126</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
@@ -13722,7 +17368,7 @@
       <c r="K38" s="1"/>
       <c r="L38" s="5"/>
       <c r="M38" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>5</v>
@@ -13735,14 +17381,14 @@
       <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="5" t="s">
         <v>127</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>27</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -13752,7 +17398,7 @@
       <c r="K39" s="1"/>
       <c r="L39" s="5"/>
       <c r="M39" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>5</v>
@@ -13765,14 +17411,14 @@
       <c r="B40" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="5" t="s">
         <v>128</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -13782,7 +17428,7 @@
       <c r="K40" s="1"/>
       <c r="L40" s="5"/>
       <c r="M40" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>5</v>
@@ -13795,14 +17441,14 @@
       <c r="B41" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="5" t="s">
         <v>129</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>29</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -13812,7 +17458,7 @@
       <c r="K41" s="1"/>
       <c r="L41" s="5"/>
       <c r="M41" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>5</v>
@@ -13825,17 +17471,17 @@
       <c r="B42" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="5" t="s">
         <v>130</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -13844,7 +17490,7 @@
       <c r="K42" s="1"/>
       <c r="L42" s="5"/>
       <c r="M42" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>5</v>
@@ -13857,14 +17503,14 @@
       <c r="B43" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="5" t="s">
         <v>131</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>42</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -13874,7 +17520,7 @@
       <c r="K43" s="1"/>
       <c r="L43" s="5"/>
       <c r="M43" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>5</v>
@@ -13887,14 +17533,14 @@
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="5" t="s">
         <v>132</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -13904,7 +17550,7 @@
       <c r="K44" s="1"/>
       <c r="L44" s="5"/>
       <c r="M44" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>5</v>
@@ -13917,14 +17563,14 @@
       <c r="B45" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="5" t="s">
         <v>133</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -13934,7 +17580,7 @@
       <c r="K45" s="1"/>
       <c r="L45" s="5"/>
       <c r="M45" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>5</v>
@@ -13947,17 +17593,17 @@
       <c r="B46" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="5" t="s">
         <v>134</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>33</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -13966,7 +17612,7 @@
       <c r="K46" s="1"/>
       <c r="L46" s="5"/>
       <c r="M46" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>5</v>
@@ -13979,14 +17625,14 @@
       <c r="B47" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="5" t="s">
         <v>135</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>34</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -13995,7 +17641,7 @@
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="M47" s="1"/>
       <c r="N47" s="1" t="s">
@@ -14009,14 +17655,14 @@
       <c r="B48" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="5" t="s">
         <v>136</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -14025,7 +17671,7 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="5" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="M48" s="1"/>
       <c r="N48" s="1" t="s">
@@ -14039,14 +17685,14 @@
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" s="5" t="s">
         <v>137</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>38</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -14055,7 +17701,7 @@
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="5" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M49" s="1"/>
       <c r="N49" s="1" t="s">
@@ -14069,14 +17715,14 @@
       <c r="B50" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="5" t="s">
         <v>138</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>36</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -14086,7 +17732,7 @@
       <c r="K50" s="1"/>
       <c r="L50" s="5"/>
       <c r="M50" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N50" s="1" t="s">
         <v>5</v>
@@ -14099,14 +17745,14 @@
       <c r="B51" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="5" t="s">
         <v>139</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>37</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -14116,7 +17762,7 @@
       <c r="K51" s="1"/>
       <c r="L51" s="5"/>
       <c r="M51" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N51" s="1" t="s">
         <v>5</v>
@@ -14129,17 +17775,17 @@
       <c r="B52" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C52" s="5" t="s">
         <v>140</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="1"/>
@@ -14148,30 +17794,30 @@
       <c r="K52" s="1"/>
       <c r="L52" s="5"/>
       <c r="M52" s="1" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="5" t="s">
         <v>141</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="1"/>
@@ -14180,7 +17826,7 @@
       <c r="K53" s="1"/>
       <c r="L53" s="5"/>
       <c r="M53" s="6" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>5</v>
@@ -14193,14 +17839,14 @@
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -14210,7 +17856,7 @@
       <c r="K54" s="1"/>
       <c r="L54" s="5"/>
       <c r="M54" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>5</v>
@@ -14223,14 +17869,14 @@
       <c r="B55" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C55" s="5" t="s">
         <v>143</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>43</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -14240,7 +17886,7 @@
       <c r="K55" s="1"/>
       <c r="L55" s="5"/>
       <c r="M55" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>5</v>
@@ -14253,14 +17899,14 @@
       <c r="B56" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="5" t="s">
         <v>144</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -14270,7 +17916,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="5"/>
       <c r="M56" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="N56" s="1" t="s">
         <v>5</v>
@@ -14283,17 +17929,17 @@
       <c r="B57" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" s="5" t="s">
         <v>145</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -14302,7 +17948,7 @@
       <c r="K57" s="1"/>
       <c r="L57" s="5"/>
       <c r="M57" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="N57" s="1" t="s">
         <v>5</v>
@@ -14315,17 +17961,17 @@
       <c r="B58" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C58" s="5" t="s">
         <v>146</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>46</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -14334,7 +17980,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="5"/>
       <c r="M58" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N58" s="1" t="s">
         <v>5</v>
@@ -14347,17 +17993,17 @@
       <c r="B59" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C59" s="5" t="s">
         <v>147</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>47</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -14365,7 +18011,7 @@
       <c r="K59" s="1"/>
       <c r="L59" s="5"/>
       <c r="M59" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N59" s="1" t="s">
         <v>5</v>
@@ -14378,30 +18024,30 @@
       <c r="B60" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C60" s="5" t="s">
         <v>148</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>48</v>
       </c>
       <c r="E60" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="H60" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="5"/>
       <c r="M60" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N60" s="1" t="s">
         <v>5</v>
@@ -14414,30 +18060,30 @@
       <c r="B61" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C61" s="15" t="s">
+      <c r="C61" s="5" t="s">
         <v>149</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>49</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="5"/>
       <c r="M61" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>5</v>
@@ -14450,14 +18096,14 @@
       <c r="B62" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C62" s="15" t="s">
+      <c r="C62" s="5" t="s">
         <v>150</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>50</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -14467,7 +18113,7 @@
       <c r="K62" s="1"/>
       <c r="L62" s="5"/>
       <c r="M62" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N62" s="1" t="s">
         <v>5</v>
@@ -14480,28 +18126,28 @@
       <c r="B63" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" s="5" t="s">
         <v>151</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>51</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="5"/>
       <c r="M63" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="N63" s="1" t="s">
         <v>5</v>
@@ -14514,14 +18160,14 @@
       <c r="B64" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="C64" s="5" t="s">
         <v>152</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>74</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -14531,27 +18177,27 @@
       <c r="K64" s="1"/>
       <c r="L64" s="5"/>
       <c r="M64" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N64" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:14" s="8" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C65" s="15" t="s">
+      <c r="C65" s="5" t="s">
         <v>153</v>
       </c>
       <c r="D65" s="11" t="s">
         <v>52</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F65" s="12"/>
       <c r="G65" s="12"/>
@@ -14561,7 +18207,7 @@
       <c r="K65" s="12"/>
       <c r="L65" s="12"/>
       <c r="M65" s="11" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="N65" s="1" t="s">
         <v>5</v>
@@ -14574,14 +18220,14 @@
       <c r="B66" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C66" s="15" t="s">
+      <c r="C66" s="5" t="s">
         <v>154</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>53</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
@@ -14591,7 +18237,7 @@
       <c r="K66" s="1"/>
       <c r="L66" s="5"/>
       <c r="M66" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="N66" s="1" t="s">
         <v>5</v>
@@ -14604,14 +18250,14 @@
       <c r="B67" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C67" s="15" t="s">
+      <c r="C67" s="5" t="s">
         <v>155</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>54</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
@@ -14621,7 +18267,7 @@
       <c r="K67" s="1"/>
       <c r="L67" s="5"/>
       <c r="M67" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>5</v>
@@ -14634,17 +18280,17 @@
       <c r="B68" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C68" s="15" t="s">
+      <c r="C68" s="5" t="s">
         <v>156</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>55</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -14653,7 +18299,7 @@
       <c r="K68" s="1"/>
       <c r="L68" s="5"/>
       <c r="M68" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="N68" s="1" t="s">
         <v>5</v>
@@ -14666,17 +18312,17 @@
       <c r="B69" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C69" s="15" t="s">
+      <c r="C69" s="5" t="s">
         <v>157</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>56</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -14685,7 +18331,7 @@
       <c r="K69" s="1"/>
       <c r="L69" s="5"/>
       <c r="M69" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N69" s="1" t="s">
         <v>5</v>
@@ -14698,17 +18344,17 @@
       <c r="B70" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C70" s="15" t="s">
+      <c r="C70" s="5" t="s">
         <v>158</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>57</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -14716,7 +18362,7 @@
       <c r="K70" s="1"/>
       <c r="L70" s="5"/>
       <c r="M70" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N70" s="1" t="s">
         <v>5</v>
@@ -14729,30 +18375,30 @@
       <c r="B71" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C71" s="15" t="s">
+      <c r="C71" s="5" t="s">
         <v>159</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>58</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G71" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="H71" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="5"/>
       <c r="M71" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N71" s="1" t="s">
         <v>5</v>
@@ -14765,30 +18411,30 @@
       <c r="B72" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="C72" s="5" t="s">
         <v>160</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>68</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="G72" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="H72" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="5"/>
       <c r="M72" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N72" s="1" t="s">
         <v>5</v>
@@ -14801,14 +18447,14 @@
       <c r="B73" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C73" s="15" t="s">
+      <c r="C73" s="5" t="s">
         <v>161</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F73" s="1"/>
       <c r="H73" s="1"/>
@@ -14817,7 +18463,7 @@
       <c r="K73" s="1"/>
       <c r="L73" s="5"/>
       <c r="M73" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N73" s="1" t="s">
         <v>5</v>
@@ -14830,28 +18476,28 @@
       <c r="B74" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C74" s="15" t="s">
+      <c r="C74" s="5" t="s">
         <v>162</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>60</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="5"/>
       <c r="M74" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="N74" s="1" t="s">
         <v>5</v>
@@ -14864,14 +18510,14 @@
       <c r="B75" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C75" s="15" t="s">
+      <c r="C75" s="5" t="s">
         <v>163</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>73</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
@@ -14881,7 +18527,7 @@
       <c r="K75" s="1"/>
       <c r="L75" s="5"/>
       <c r="M75" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N75" s="1" t="s">
         <v>5</v>
@@ -14894,14 +18540,14 @@
       <c r="B76" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="C76" s="5" t="s">
         <v>164</v>
       </c>
       <c r="D76" s="11" t="s">
         <v>61</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F76" s="12"/>
       <c r="G76" s="12"/>
@@ -14911,7 +18557,7 @@
       <c r="K76" s="12"/>
       <c r="L76" s="12"/>
       <c r="M76" s="11" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="N76" s="1" t="s">
         <v>5</v>
@@ -14924,14 +18570,14 @@
       <c r="B77" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C77" s="15" t="s">
+      <c r="C77" s="5" t="s">
         <v>165</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>62</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -14941,7 +18587,7 @@
       <c r="K77" s="1"/>
       <c r="L77" s="5"/>
       <c r="M77" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="N77" s="1" t="s">
         <v>5</v>
@@ -14954,14 +18600,14 @@
       <c r="B78" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C78" s="15" t="s">
+      <c r="C78" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>63</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
@@ -14971,7 +18617,7 @@
       <c r="K78" s="1"/>
       <c r="L78" s="5"/>
       <c r="M78" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="N78" s="1" t="s">
         <v>5</v>
@@ -14984,17 +18630,17 @@
       <c r="B79" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C79" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>64</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -15003,7 +18649,7 @@
       <c r="K79" s="1"/>
       <c r="L79" s="5"/>
       <c r="M79" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="N79" s="1" t="s">
         <v>5</v>
@@ -15016,17 +18662,17 @@
       <c r="B80" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C80" s="15" t="s">
+      <c r="C80" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>65</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
@@ -15035,7 +18681,7 @@
       <c r="K80" s="1"/>
       <c r="L80" s="5"/>
       <c r="M80" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N80" s="1" t="s">
         <v>5</v>
@@ -15048,17 +18694,17 @@
       <c r="B81" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C81" s="15" t="s">
+      <c r="C81" s="5" t="s">
         <v>169</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>66</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -15066,7 +18712,7 @@
       <c r="K81" s="1"/>
       <c r="L81" s="5"/>
       <c r="M81" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N81" s="1" t="s">
         <v>5</v>
@@ -15079,30 +18725,30 @@
       <c r="B82" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C82" s="15" t="s">
+      <c r="C82" s="5" t="s">
         <v>170</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="5"/>
       <c r="M82" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N82" s="1" t="s">
         <v>5</v>
@@ -15115,30 +18761,30 @@
       <c r="B83" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C83" s="15" t="s">
+      <c r="C83" s="5" t="s">
         <v>171</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
       <c r="L83" s="5"/>
       <c r="M83" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N83" s="1" t="s">
         <v>5</v>
@@ -15151,14 +18797,14 @@
       <c r="B84" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C84" s="15" t="s">
+      <c r="C84" s="5" t="s">
         <v>172</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>70</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F84" s="1"/>
       <c r="H84" s="1"/>
@@ -15167,7 +18813,7 @@
       <c r="K84" s="1"/>
       <c r="L84" s="5"/>
       <c r="M84" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N84" s="1" t="s">
         <v>5</v>
@@ -15180,28 +18826,28 @@
       <c r="B85" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C85" s="15" t="s">
+      <c r="C85" s="5" t="s">
         <v>173</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>71</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F85" s="14" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="5"/>
       <c r="M85" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="N85" s="1" t="s">
         <v>5</v>
@@ -15214,14 +18860,14 @@
       <c r="B86" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C86" s="15" t="s">
+      <c r="C86" s="5" t="s">
         <v>174</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>72</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
@@ -15231,27 +18877,27 @@
       <c r="K86" s="1"/>
       <c r="L86" s="5"/>
       <c r="M86" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N86" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="15" t="s">
+      <c r="C87" s="5" t="s">
         <v>175</v>
       </c>
       <c r="D87" s="11" t="s">
         <v>75</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F87" s="12"/>
       <c r="G87" s="12"/>
@@ -15261,7 +18907,7 @@
       <c r="K87" s="12"/>
       <c r="L87" s="12"/>
       <c r="M87" s="11" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="N87" s="1" t="s">
         <v>5</v>
@@ -15274,14 +18920,14 @@
       <c r="B88" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C88" s="15" t="s">
+      <c r="C88" s="5" t="s">
         <v>176</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>76</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
@@ -15291,7 +18937,7 @@
       <c r="K88" s="1"/>
       <c r="L88" s="5"/>
       <c r="M88" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="N88" s="1" t="s">
         <v>5</v>
@@ -15304,14 +18950,14 @@
       <c r="B89" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C89" s="15" t="s">
+      <c r="C89" s="5" t="s">
         <v>177</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>77</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
@@ -15321,7 +18967,7 @@
       <c r="K89" s="1"/>
       <c r="L89" s="5"/>
       <c r="M89" s="1" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="N89" s="1" t="s">
         <v>5</v>
@@ -15334,17 +18980,17 @@
       <c r="B90" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C90" s="15" t="s">
+      <c r="C90" s="5" t="s">
         <v>178</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>78</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
@@ -15353,7 +18999,7 @@
       <c r="K90" s="1"/>
       <c r="L90" s="5"/>
       <c r="M90" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="N90" s="1" t="s">
         <v>5</v>
@@ -15366,17 +19012,17 @@
       <c r="B91" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C91" s="15" t="s">
+      <c r="C91" s="5" t="s">
         <v>179</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
@@ -15385,7 +19031,7 @@
       <c r="K91" s="1"/>
       <c r="L91" s="5"/>
       <c r="M91" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N91" s="1" t="s">
         <v>5</v>
@@ -15398,17 +19044,17 @@
       <c r="B92" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C92" s="15" t="s">
+      <c r="C92" s="5" t="s">
         <v>180</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>80</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -15416,7 +19062,7 @@
       <c r="K92" s="1"/>
       <c r="L92" s="5"/>
       <c r="M92" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N92" s="1" t="s">
         <v>5</v>
@@ -15429,30 +19075,30 @@
       <c r="B93" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C93" s="15" t="s">
+      <c r="C93" s="5" t="s">
         <v>181</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>81</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
       <c r="L93" s="5"/>
       <c r="M93" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N93" s="1" t="s">
         <v>5</v>
@@ -15465,30 +19111,30 @@
       <c r="B94" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C94" s="15" t="s">
+      <c r="C94" s="5" t="s">
         <v>182</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>82</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F94" s="14" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
       <c r="L94" s="5"/>
       <c r="M94" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N94" s="1" t="s">
         <v>5</v>
@@ -15501,14 +19147,14 @@
       <c r="B95" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C95" s="15" t="s">
+      <c r="C95" s="5" t="s">
         <v>183</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>83</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F95" s="1"/>
       <c r="H95" s="1"/>
@@ -15517,7 +19163,7 @@
       <c r="K95" s="1"/>
       <c r="L95" s="5"/>
       <c r="M95" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N95" s="1" t="s">
         <v>5</v>
@@ -15530,28 +19176,28 @@
       <c r="B96" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C96" s="15" t="s">
+      <c r="C96" s="5" t="s">
         <v>184</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>84</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F96" s="14" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="G96" s="1"/>
       <c r="H96" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
       <c r="L96" s="5"/>
       <c r="M96" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="N96" s="1" t="s">
         <v>5</v>
@@ -15564,14 +19210,14 @@
       <c r="B97" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C97" s="15" t="s">
+      <c r="C97" s="5" t="s">
         <v>185</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>85</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
@@ -15581,27 +19227,27 @@
       <c r="K97" s="1"/>
       <c r="L97" s="5"/>
       <c r="M97" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N97" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C98" s="15" t="s">
+      <c r="C98" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D98" s="13" t="s">
         <v>86</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
@@ -15611,7 +19257,7 @@
       <c r="K98" s="5"/>
       <c r="L98" s="5"/>
       <c r="M98" s="13" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="N98" s="1" t="s">
         <v>5</v>
@@ -15624,14 +19270,14 @@
       <c r="B99" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C99" s="15" t="s">
+      <c r="C99" s="5" t="s">
         <v>187</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>87</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
@@ -15641,7 +19287,7 @@
       <c r="K99" s="1"/>
       <c r="L99" s="5"/>
       <c r="M99" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N99" s="1" t="s">
         <v>5</v>
@@ -15654,14 +19300,14 @@
       <c r="B100" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C100" s="15" t="s">
+      <c r="C100" s="5" t="s">
         <v>188</v>
       </c>
       <c r="D100" s="11" t="s">
         <v>88</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F100" s="12"/>
       <c r="G100" s="12"/>
@@ -15671,27 +19317,27 @@
       <c r="K100" s="12"/>
       <c r="L100" s="12"/>
       <c r="M100" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="N100" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C101" s="15" t="s">
+      <c r="C101" s="5" t="s">
         <v>189</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>89</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>345</v>
+        <v>542</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
@@ -15701,7 +19347,7 @@
       <c r="K101" s="1"/>
       <c r="L101" s="5"/>
       <c r="M101" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N101" s="1" t="s">
         <v>5</v>
@@ -15714,14 +19360,14 @@
       <c r="B102" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C102" s="15" t="s">
+      <c r="C102" s="5" t="s">
         <v>190</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
@@ -15731,7 +19377,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="5"/>
       <c r="M102" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="N102" s="1" t="s">
         <v>5</v>
@@ -15744,14 +19390,14 @@
       <c r="B103" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C103" s="15" t="s">
+      <c r="C103" s="5" t="s">
         <v>191</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>197</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
@@ -15761,7 +19407,7 @@
       <c r="K103" s="1"/>
       <c r="L103" s="5"/>
       <c r="M103" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="N103" s="1" t="s">
         <v>5</v>
@@ -15774,17 +19420,17 @@
       <c r="B104" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C104" s="15" t="s">
+      <c r="C104" s="5" t="s">
         <v>192</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>196</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="G104" s="1"/>
       <c r="H104" s="1"/>
@@ -15793,7 +19439,7 @@
       <c r="K104" s="1"/>
       <c r="L104" s="5"/>
       <c r="M104" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="N104" s="1" t="s">
         <v>5</v>
@@ -15806,17 +19452,17 @@
       <c r="B105" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C105" s="15" t="s">
+      <c r="C105" s="5" t="s">
         <v>193</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>195</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G105" s="1"/>
       <c r="H105" s="1"/>
@@ -15825,7 +19471,7 @@
       <c r="K105" s="1"/>
       <c r="L105" s="5"/>
       <c r="M105" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N105" s="1" t="s">
         <v>5</v>
@@ -15838,17 +19484,17 @@
       <c r="B106" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C106" s="15" t="s">
+      <c r="C106" s="5" t="s">
         <v>205</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>194</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
@@ -15856,7 +19502,7 @@
       <c r="K106" s="1"/>
       <c r="L106" s="5"/>
       <c r="M106" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N106" s="1" t="s">
         <v>5</v>
@@ -15869,28 +19515,28 @@
       <c r="B107" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C107" s="15" t="s">
+      <c r="C107" s="5" t="s">
         <v>206</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>198</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="G107" s="1"/>
       <c r="H107" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="5"/>
       <c r="M107" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="N107" s="1" t="s">
         <v>5</v>
@@ -15903,14 +19549,14 @@
       <c r="B108" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C108" s="15" t="s">
+      <c r="C108" s="5" t="s">
         <v>207</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>199</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
@@ -15920,7 +19566,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="5"/>
       <c r="M108" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="N108" s="1" t="s">
         <v>5</v>
@@ -15933,28 +19579,28 @@
       <c r="B109" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C109" s="15" t="s">
+      <c r="C109" s="5" t="s">
         <v>208</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>200</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="G109" s="1"/>
       <c r="H109" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
       <c r="L109" s="5"/>
       <c r="M109" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N109" s="1" t="s">
         <v>5</v>
@@ -15967,14 +19613,14 @@
       <c r="B110" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C110" s="15" t="s">
+      <c r="C110" s="5" t="s">
         <v>209</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>201</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
@@ -15984,7 +19630,7 @@
       <c r="K110" s="1"/>
       <c r="L110" s="5"/>
       <c r="M110" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N110" s="1" t="s">
         <v>5</v>
@@ -15997,14 +19643,14 @@
       <c r="B111" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C111" s="15" t="s">
+      <c r="C111" s="5" t="s">
         <v>210</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>202</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
@@ -16013,7 +19659,7 @@
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
       <c r="L111" s="5" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="M111" s="1"/>
       <c r="N111" s="1" t="s">
@@ -16027,14 +19673,14 @@
       <c r="B112" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C112" s="15" t="s">
+      <c r="C112" s="5" t="s">
         <v>211</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>203</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
@@ -16044,7 +19690,7 @@
       <c r="K112" s="1"/>
       <c r="L112" s="5"/>
       <c r="M112" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="N112" s="1" t="s">
         <v>5</v>
@@ -16057,14 +19703,14 @@
       <c r="B113" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C113" s="15" t="s">
+      <c r="C113" s="5" t="s">
         <v>212</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>204</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
@@ -16074,7 +19720,7 @@
       <c r="K113" s="1"/>
       <c r="L113" s="5"/>
       <c r="M113" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N113" s="1" t="s">
         <v>5</v>
@@ -16087,14 +19733,14 @@
       <c r="B114" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C114" s="15" t="s">
+      <c r="C114" s="5" t="s">
         <v>213</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>217</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
@@ -16117,28 +19763,28 @@
       <c r="B115" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C115" s="15" t="s">
+      <c r="C115" s="5" t="s">
         <v>214</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>221</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
       <c r="K115" s="1"/>
       <c r="L115" s="5"/>
       <c r="M115" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N115" s="1" t="s">
         <v>5</v>
@@ -16151,14 +19797,14 @@
       <c r="B116" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C116" s="15" t="s">
+      <c r="C116" s="5" t="s">
         <v>215</v>
       </c>
       <c r="D116" s="11" t="s">
         <v>222</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
@@ -16168,27 +19814,27 @@
       <c r="K116" s="1"/>
       <c r="L116" s="5"/>
       <c r="M116" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="N116" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" s="5" t="s">
         <v>216</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>223</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>469</v>
+        <v>550</v>
       </c>
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
@@ -16198,7 +19844,7 @@
       <c r="K117" s="1"/>
       <c r="L117" s="5"/>
       <c r="M117" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="N117" s="1" t="s">
         <v>5</v>
@@ -16211,14 +19857,14 @@
       <c r="B118" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C118" s="5" t="s">
         <v>218</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>224</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
@@ -16228,7 +19874,7 @@
       <c r="K118" s="1"/>
       <c r="L118" s="5"/>
       <c r="M118" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="N118" s="1" t="s">
         <v>5</v>
@@ -16241,18 +19887,18 @@
       <c r="B119" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C119" s="5" t="s">
         <v>219</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>225</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F119" s="1"/>
       <c r="G119" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
@@ -16260,7 +19906,7 @@
       <c r="K119" s="1"/>
       <c r="L119" s="5"/>
       <c r="M119" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N119" s="1" t="s">
         <v>5</v>
@@ -16273,50 +19919,50 @@
       <c r="B120" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C120" s="5" t="s">
         <v>220</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>226</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
       <c r="I120" s="1" t="s">
-        <v>477</v>
+        <v>525</v>
       </c>
       <c r="J120" s="1"/>
       <c r="K120" s="1"/>
       <c r="L120" s="5"/>
       <c r="M120" s="1" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="N120" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" s="5" t="s">
         <v>234</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>227</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>481</v>
+        <v>527</v>
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
@@ -16324,7 +19970,7 @@
       <c r="K121" s="1"/>
       <c r="L121" s="5"/>
       <c r="M121" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N121" s="1" t="s">
         <v>5</v>
@@ -16337,26 +19983,26 @@
       <c r="B122" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" s="5" t="s">
         <v>235</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>228</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
       <c r="J122" s="1" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="K122" s="1"/>
       <c r="L122" s="5"/>
       <c r="M122" s="1" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="N122" s="1" t="s">
         <v>5</v>
@@ -16369,14 +20015,14 @@
       <c r="B123" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C123" s="5" t="s">
         <v>236</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>229</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
@@ -16384,11 +20030,11 @@
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
       <c r="K123" s="1" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="L123" s="5"/>
       <c r="M123" s="1" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="N123" s="1" t="s">
         <v>5</v>
@@ -16401,14 +20047,14 @@
       <c r="B124" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C124" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>230</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
@@ -16416,11 +20062,11 @@
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
       <c r="K124" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="L124" s="5"/>
       <c r="M124" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="N124" s="1" t="s">
         <v>5</v>
@@ -16433,14 +20079,14 @@
       <c r="B125" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" s="5" t="s">
         <v>238</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>231</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
@@ -16450,7 +20096,7 @@
       <c r="K125" s="1"/>
       <c r="L125" s="5"/>
       <c r="M125" s="2" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="N125" s="1" t="s">
         <v>5</v>
@@ -16463,14 +20109,14 @@
       <c r="B126" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C126" s="5" t="s">
         <v>239</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>232</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
@@ -16480,7 +20126,7 @@
       <c r="K126" s="1"/>
       <c r="L126" s="5"/>
       <c r="M126" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="N126" s="1" t="s">
         <v>5</v>
@@ -16493,14 +20139,14 @@
       <c r="B127" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C127" s="5" t="s">
         <v>240</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>233</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
@@ -16510,27 +20156,27 @@
       <c r="K127" s="1"/>
       <c r="L127" s="5"/>
       <c r="M127" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="N127" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:14" ht="145" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:14" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C128" s="5" t="s">
         <v>241</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
@@ -16540,27 +20186,27 @@
       <c r="K128" s="1"/>
       <c r="L128" s="5"/>
       <c r="M128" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="N128" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C129" s="5" t="s">
         <v>242</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="F129" s="1"/>
       <c r="G129" s="1"/>
@@ -16570,27 +20216,27 @@
       <c r="K129" s="1"/>
       <c r="L129" s="5"/>
       <c r="M129" s="1" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="N129" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C130" s="5" t="s">
         <v>243</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>517</v>
+        <v>247</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>509</v>
       </c>
       <c r="F130" s="1"/>
       <c r="G130" s="1"/>
@@ -16600,7 +20246,7 @@
       <c r="K130" s="1"/>
       <c r="L130" s="5"/>
       <c r="M130" s="1" t="s">
-        <v>10</v>
+        <v>510</v>
       </c>
       <c r="N130" s="1" t="s">
         <v>5</v>
@@ -16613,14 +20259,14 @@
       <c r="B131" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="C131" s="5" t="s">
         <v>244</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="F131" s="1"/>
       <c r="G131" s="1"/>
@@ -16630,27 +20276,27 @@
       <c r="K131" s="1"/>
       <c r="L131" s="5"/>
       <c r="M131" s="1" t="s">
-        <v>519</v>
+        <v>451</v>
       </c>
       <c r="N131" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>245</v>
+      <c r="C132" s="5" t="s">
+        <v>250</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
@@ -16660,37 +20306,43 @@
       <c r="K132" s="1"/>
       <c r="L132" s="5"/>
       <c r="M132" s="1" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="N132" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:14" ht="232" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>252</v>
+      <c r="C133" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
       <c r="H133" s="1"/>
-      <c r="I133" s="1"/>
-      <c r="J133" s="1"/>
-      <c r="K133" s="1"/>
+      <c r="I133" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>520</v>
+      </c>
       <c r="L133" s="5"/>
       <c r="M133" s="1" t="s">
-        <v>467</v>
+        <v>319</v>
       </c>
       <c r="N133" s="1" t="s">
         <v>5</v>
@@ -16703,20 +20355,24 @@
       <c r="B134" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>253</v>
+      <c r="C134" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="E134" s="1"/>
+        <v>258</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>512</v>
+      </c>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
       <c r="H134" s="1"/>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
       <c r="K134" s="1"/>
-      <c r="L134" s="5"/>
+      <c r="L134" s="5" t="s">
+        <v>470</v>
+      </c>
       <c r="M134" s="1"/>
       <c r="N134" s="1" t="s">
         <v>5</v>
@@ -16729,20 +20385,24 @@
       <c r="B135" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>254</v>
+      <c r="C135" s="5" t="s">
+        <v>253</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="E135" s="1"/>
+        <v>259</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>514</v>
+      </c>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1"/>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
-      <c r="L135" s="5"/>
+      <c r="L135" s="5" t="s">
+        <v>517</v>
+      </c>
       <c r="M135" s="1"/>
       <c r="N135" s="1" t="s">
         <v>5</v>
@@ -16755,20 +20415,24 @@
       <c r="B136" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>255</v>
+      <c r="C136" s="5" t="s">
+        <v>254</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="E136" s="1"/>
+        <v>260</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>515</v>
+      </c>
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
       <c r="H136" s="1"/>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
       <c r="K136" s="1"/>
-      <c r="L136" s="5"/>
+      <c r="L136" s="5" t="s">
+        <v>471</v>
+      </c>
       <c r="M136" s="1"/>
       <c r="N136" s="1" t="s">
         <v>5</v>
@@ -16781,39 +20445,45 @@
       <c r="B137" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>256</v>
+      <c r="C137" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E137" s="1"/>
+        <v>261</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>516</v>
+      </c>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
       <c r="K137" s="1"/>
-      <c r="L137" s="5"/>
+      <c r="L137" s="5" t="s">
+        <v>472</v>
+      </c>
       <c r="M137" s="1"/>
       <c r="N137" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>257</v>
+      <c r="C138" s="5" t="s">
+        <v>256</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="E138" s="1"/>
+        <v>262</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>521</v>
+      </c>
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
       <c r="H138" s="1"/>
@@ -16821,25 +20491,29 @@
       <c r="J138" s="1"/>
       <c r="K138" s="1"/>
       <c r="L138" s="5"/>
-      <c r="M138" s="1"/>
+      <c r="M138" s="1" t="s">
+        <v>510</v>
+      </c>
       <c r="N138" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>258</v>
+      <c r="C139" s="5" t="s">
+        <v>274</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="E139" s="1"/>
+        <v>263</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>522</v>
+      </c>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
@@ -16847,59 +20521,81 @@
       <c r="J139" s="1"/>
       <c r="K139" s="1"/>
       <c r="L139" s="5"/>
-      <c r="M139" s="1"/>
+      <c r="M139" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="N139" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:14" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>276</v>
+      <c r="C140" s="5" t="s">
+        <v>275</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="E140" s="1"/>
+        <v>264</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>523</v>
+      </c>
       <c r="F140" s="1"/>
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
-      <c r="I140" s="1"/>
-      <c r="J140" s="1"/>
-      <c r="K140" s="1"/>
+      <c r="I140" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>520</v>
+      </c>
       <c r="L140" s="5"/>
-      <c r="M140" s="1"/>
+      <c r="M140" s="1" t="s">
+        <v>465</v>
+      </c>
       <c r="N140" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>277</v>
+      <c r="C141" s="5" t="s">
+        <v>276</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="E141" s="1"/>
+        <v>265</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="F141" s="1"/>
       <c r="G141" s="1"/>
       <c r="H141" s="1"/>
-      <c r="I141" s="1"/>
-      <c r="J141" s="1"/>
-      <c r="K141" s="1"/>
+      <c r="I141" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="K141" s="1" t="s">
+        <v>531</v>
+      </c>
       <c r="L141" s="5"/>
-      <c r="M141" s="1"/>
+      <c r="M141" s="1" t="s">
+        <v>321</v>
+      </c>
       <c r="N141" s="1" t="s">
         <v>5</v>
       </c>
@@ -16911,13 +20607,15 @@
       <c r="B142" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C142" s="1" t="s">
-        <v>278</v>
+      <c r="C142" s="5" t="s">
+        <v>277</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="E142" s="1"/>
+        <v>266</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>361</v>
+      </c>
       <c r="F142" s="1"/>
       <c r="G142" s="1"/>
       <c r="H142" s="1"/>
@@ -16925,25 +20623,29 @@
       <c r="J142" s="1"/>
       <c r="K142" s="1"/>
       <c r="L142" s="5"/>
-      <c r="M142" s="1"/>
+      <c r="M142" s="1" t="s">
+        <v>532</v>
+      </c>
       <c r="N142" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>279</v>
+      <c r="C143" s="5" t="s">
+        <v>278</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="E143" s="1"/>
+        <v>267</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>536</v>
+      </c>
       <c r="F143" s="1"/>
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
@@ -16951,7 +20653,9 @@
       <c r="J143" s="1"/>
       <c r="K143" s="1"/>
       <c r="L143" s="5"/>
-      <c r="M143" s="1"/>
+      <c r="M143" s="15" t="s">
+        <v>548</v>
+      </c>
       <c r="N143" s="1" t="s">
         <v>5</v>
       </c>
@@ -16963,13 +20667,15 @@
       <c r="B144" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C144" s="1" t="s">
-        <v>280</v>
+      <c r="C144" s="5" t="s">
+        <v>279</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="E144" s="1"/>
+        <v>268</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>537</v>
+      </c>
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
       <c r="H144" s="1"/>
@@ -16977,25 +20683,29 @@
       <c r="J144" s="1"/>
       <c r="K144" s="1"/>
       <c r="L144" s="5"/>
-      <c r="M144" s="1"/>
+      <c r="M144" s="15" t="s">
+        <v>549</v>
+      </c>
       <c r="N144" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C145" s="1" t="s">
-        <v>281</v>
+      <c r="C145" s="5" t="s">
+        <v>280</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="E145" s="1"/>
+        <v>269</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>538</v>
+      </c>
       <c r="F145" s="1"/>
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
@@ -17003,7 +20713,9 @@
       <c r="J145" s="1"/>
       <c r="K145" s="1"/>
       <c r="L145" s="5"/>
-      <c r="M145" s="1"/>
+      <c r="M145" s="15" t="s">
+        <v>539</v>
+      </c>
       <c r="N145" s="1" t="s">
         <v>5</v>
       </c>
@@ -17015,13 +20727,15 @@
       <c r="B146" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>282</v>
+      <c r="C146" s="5" t="s">
+        <v>281</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="E146" s="1"/>
+        <v>270</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>533</v>
+      </c>
       <c r="F146" s="1"/>
       <c r="G146" s="1"/>
       <c r="H146" s="1"/>
@@ -17029,25 +20743,29 @@
       <c r="J146" s="1"/>
       <c r="K146" s="1"/>
       <c r="L146" s="5"/>
-      <c r="M146" s="1"/>
+      <c r="M146" s="15" t="s">
+        <v>540</v>
+      </c>
       <c r="N146" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>283</v>
+      <c r="C147" s="5" t="s">
+        <v>282</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="E147" s="1"/>
+        <v>271</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="F147" s="1"/>
       <c r="G147" s="1"/>
       <c r="H147" s="1"/>
@@ -17055,25 +20773,29 @@
       <c r="J147" s="1"/>
       <c r="K147" s="1"/>
       <c r="L147" s="5"/>
-      <c r="M147" s="1"/>
+      <c r="M147" s="15" t="s">
+        <v>285</v>
+      </c>
       <c r="N147" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>284</v>
+      <c r="C148" s="5" t="s">
+        <v>283</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="E148" s="1"/>
+        <v>272</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>535</v>
+      </c>
       <c r="F148" s="1"/>
       <c r="G148" s="1"/>
       <c r="H148" s="1"/>
@@ -17081,7 +20803,9 @@
       <c r="J148" s="1"/>
       <c r="K148" s="1"/>
       <c r="L148" s="5"/>
-      <c r="M148" s="1"/>
+      <c r="M148" s="15" t="s">
+        <v>10</v>
+      </c>
       <c r="N148" s="1" t="s">
         <v>5</v>
       </c>
@@ -17093,13 +20817,15 @@
       <c r="B149" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C149" s="1" t="s">
-        <v>285</v>
+      <c r="C149" s="5" t="s">
+        <v>284</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="E149" s="1"/>
+        <v>273</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>340</v>
+      </c>
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
       <c r="H149" s="1"/>
@@ -17107,39 +20833,15 @@
       <c r="J149" s="1"/>
       <c r="K149" s="1"/>
       <c r="L149" s="5"/>
-      <c r="M149" s="1"/>
+      <c r="M149" s="15" t="s">
+        <v>541</v>
+      </c>
       <c r="N149" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A150" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="E150" s="1"/>
-      <c r="F150" s="1"/>
-      <c r="G150" s="1"/>
-      <c r="H150" s="1"/>
-      <c r="I150" s="1"/>
-      <c r="J150" s="1"/>
-      <c r="K150" s="1"/>
-      <c r="L150" s="5"/>
-      <c r="M150" s="1"/>
-      <c r="N150" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N150" xr:uid="{69A0187B-E061-4912-A527-D651D3F0111B}"/>
+  <autoFilter ref="A1:N149" xr:uid="{69A0187B-E061-4912-A527-D651D3F0111B}"/>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/testdata/Modules/09_MyWebSite/MyWebSite/01_MyWebSiteTest.xlsx
+++ b/src/test/resources/testdata/Modules/09_MyWebSite/MyWebSite/01_MyWebSiteTest.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/src/test/resources/testdata/Modules/09_MyWebSite/MyWebSite/01_MyWebSiteTest.xlsx
+++ b/src/test/resources/testdata/Modules/09_MyWebSite/MyWebSite/01_MyWebSiteTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\09_MyWebSite\MyWebSite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71063F75-DF33-4AA9-9EC2-CD3DC3180DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87876D0-F6B1-4E4D-B7C4-FDE919B11B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="555">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -10577,6 +10577,25 @@
   <si>
     <t>verify_mywebsite_webversion_status
 navigatebacktodashboardpage</t>
+  </si>
+  <si>
+    <t>owners_clickon_cancelbtn
+owners_clickon_cancelbtn
+verify_owners_header</t>
+  </si>
+  <si>
+    <t>personalinfo_clickon_workprofessionfield
+clickon_selectyearvalue
+clickon_selectyearokbtn
+clickon_nextbtn
+clickon_nextbtn
+verify_warningtoastmsg</t>
+  </si>
+  <si>
+    <t>project_clickon_showworwin_cancelbtn
+project_clickon_showworwin_cancelbtn
+clickon_alert_dialog_yesbtn
+verify_project_header</t>
   </si>
 </sst>
 </file>
@@ -12007,7 +12026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="87" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>8</v>
       </c>
@@ -12021,7 +12040,7 @@
         <v>296</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>346</v>
+        <v>553</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -12862,7 +12881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>8</v>
       </c>
@@ -12876,7 +12895,7 @@
         <v>31</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>377</v>
+        <v>552</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -15468,7 +15487,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>8</v>
       </c>
@@ -15482,7 +15501,7 @@
         <v>233</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>487</v>
+        <v>554</v>
       </c>
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>

--- a/src/test/resources/testdata/Modules/09_MyWebSite/MyWebSite/01_MyWebSiteTest.xlsx
+++ b/src/test/resources/testdata/Modules/09_MyWebSite/MyWebSite/01_MyWebSiteTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\09_MyWebSite\MyWebSite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87876D0-F6B1-4E4D-B7C4-FDE919B11B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92056E12-8A74-44E1-AEF6-4FACDB047214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="557">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -10596,6 +10596,32 @@
 project_clickon_showworwin_cancelbtn
 clickon_alert_dialog_yesbtn
 verify_project_header</t>
+  </si>
+  <si>
+    <t>clickon_backarrowbtn
+clickon_backarrowbtn
+clickon_alert_dialog_yesbtn
+verify_pagetitle</t>
+  </si>
+  <si>
+    <t>owners_clickon_fabbtn
+owners_clickon_fabbtn
+owners_enter_name
+hidekeyboard
+owners_clickon_enterposition
+owners_select_positiondropoption
+owners_clickon_workingsince
+clickon_selectyearvalue
+clickon_selectyearokbtn
+owners_clickon_ownerphotoimage
+clickon_browsefileoption
+select_gallaryimage
+clickon_gallarydonebtn
+owners_get_enternamefieldtext
+owners_get_enterpositionfieldtext
+owners_get_experiancefieldtext
+owners_clickon_savebtn
+verify_owners_addedmember_isdisplay</t>
   </si>
 </sst>
 </file>
@@ -11814,7 +11840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -11828,7 +11854,7 @@
         <v>292</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>488</v>
+        <v>555</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -12941,7 +12967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" ht="261" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>8</v>
       </c>
@@ -12955,7 +12981,7 @@
         <v>33</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>379</v>
+        <v>556</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>374</v>

--- a/src/test/resources/testdata/Modules/09_MyWebSite/MyWebSite/01_MyWebSiteTest.xlsx
+++ b/src/test/resources/testdata/Modules/09_MyWebSite/MyWebSite/01_MyWebSiteTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\09_MyWebSite\MyWebSite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92056E12-8A74-44E1-AEF6-4FACDB047214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E7885B-F409-4A0E-A07E-E76A296513A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="559">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -10622,6 +10622,17 @@
 owners_get_experiancefieldtext
 owners_clickon_savebtn
 verify_owners_addedmember_isdisplay</t>
+  </si>
+  <si>
+    <t>MyWebSiteTest_129</t>
+  </si>
+  <si>
+    <t>wait_untiletoastmsg_disapears
+firmdetails_enter_teamsize
+hidekeyboard
+clickon_nextbtn
+clickon_nextbtn
+verify_alert_dialog_title</t>
   </si>
 </sst>
 </file>
@@ -12723,7 +12734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" ht="87" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>8</v>
       </c>
@@ -12737,7 +12748,7 @@
         <v>26</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>492</v>
+        <v>558</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>370</v>
@@ -14678,7 +14689,7 @@
       <c r="A100" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C100" s="5" t="s">
@@ -15611,7 +15622,7 @@
         <v>11</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>243</v>
+        <v>557</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>247</v>
@@ -15641,7 +15652,7 @@
         <v>11</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>248</v>
@@ -15671,7 +15682,7 @@
         <v>11</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>249</v>
@@ -15701,7 +15712,7 @@
         <v>11</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>257</v>
@@ -15737,7 +15748,7 @@
         <v>11</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>258</v>
@@ -15767,7 +15778,7 @@
         <v>11</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>259</v>
@@ -15797,7 +15808,7 @@
         <v>11</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>260</v>
@@ -15827,7 +15838,7 @@
         <v>11</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>261</v>
@@ -15857,7 +15868,7 @@
         <v>11</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>262</v>
@@ -15887,7 +15898,7 @@
         <v>11</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>263</v>
@@ -15917,7 +15928,7 @@
         <v>11</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>264</v>
@@ -15953,7 +15964,7 @@
         <v>11</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>265</v>
@@ -15989,7 +16000,7 @@
         <v>11</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>266</v>
@@ -16019,7 +16030,7 @@
         <v>11</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>267</v>
@@ -16049,7 +16060,7 @@
         <v>11</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>268</v>
@@ -16079,7 +16090,7 @@
         <v>11</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>269</v>
@@ -16109,7 +16120,7 @@
         <v>11</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>270</v>
@@ -16139,7 +16150,7 @@
         <v>11</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D147" s="6" t="s">
         <v>271</v>
@@ -16169,7 +16180,7 @@
         <v>11</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>272</v>
@@ -16199,7 +16210,7 @@
         <v>11</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D149" s="6" t="s">
         <v>273</v>

--- a/src/test/resources/testdata/Modules/09_MyWebSite/MyWebSite/01_MyWebSiteTest.xlsx
+++ b/src/test/resources/testdata/Modules/09_MyWebSite/MyWebSite/01_MyWebSiteTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\09_MyWebSite\MyWebSite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E7885B-F409-4A0E-A07E-E76A296513A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECD1804-3F8A-446B-B703-7D5FC92AE473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="560">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -10632,6 +10632,12 @@
 hidekeyboard
 clickon_nextbtn
 clickon_nextbtn
+verify_alert_dialog_title</t>
+  </si>
+  <si>
+    <t>project_add_projects
+project_clickon_submitbtn
+project_clickon_submitbtn
 verify_alert_dialog_title</t>
   </si>
 </sst>
@@ -15956,7 +15962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>8</v>
       </c>
@@ -15970,7 +15976,7 @@
         <v>265</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>524</v>
+        <v>559</v>
       </c>
       <c r="F141" s="1"/>
       <c r="G141" s="1"/>

--- a/src/test/resources/testdata/Modules/09_MyWebSite/MyWebSite/01_MyWebSiteTest.xlsx
+++ b/src/test/resources/testdata/Modules/09_MyWebSite/MyWebSite/01_MyWebSiteTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\09_MyWebSite\MyWebSite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECD1804-3F8A-446B-B703-7D5FC92AE473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88629913-7404-43EF-B638-223FF101EFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="561">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -10639,6 +10639,13 @@
 project_clickon_submitbtn
 project_clickon_submitbtn
 verify_alert_dialog_title</t>
+  </si>
+  <si>
+    <t>project_enter_showworkwin_projectname
+hidekeyboard
+project_clickon_showworwin_savebtn
+project_clickon_showworwin_savebtn
+verify_project_showworwin_stylefielderror</t>
   </si>
 </sst>
 </file>
@@ -15310,7 +15317,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>8</v>
       </c>
@@ -15324,7 +15331,7 @@
         <v>226</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>473</v>
+        <v>560</v>
       </c>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
